--- a/TC/db/Permission Matrix.xlsx
+++ b/TC/db/Permission Matrix.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2471B1E6-AC96-4018-923D-24BD1708C6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="15015" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Matrix" state="visible" r:id="rId4"/>
+    <sheet name="Matrix" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -154,14 +163,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -173,7 +182,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,8 +214,14 @@
         <fgColor rgb="FFB9FFD9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -266,54 +281,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -322,23 +348,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -349,11 +363,45 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,643 +741,638 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:O31"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
-    <col min="2" max="2" width="9.285714285714286" customWidth="1"/>
-    <col min="3" max="3" width="15.714285714285714" customWidth="1"/>
-    <col min="4" max="4" width="9.285714285714286" customWidth="1"/>
-    <col min="5" max="5" width="68.71428571428571" customWidth="1"/>
-    <col min="6" max="6" width="11.857142857142858" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="68.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="10.714285714285714" customWidth="1"/>
-    <col min="9" max="9" width="13.571428571428571" customWidth="1"/>
-    <col min="10" max="10" width="11.857142857142858" customWidth="1"/>
-    <col min="11" max="11" width="19.571428571428573" customWidth="1"/>
-    <col min="12" max="12" width="17.142857142857142" customWidth="1"/>
-    <col min="13" max="13" width="13.571428571428571" customWidth="1"/>
-    <col min="14" max="14" width="9.285714285714286" customWidth="1"/>
-    <col min="15" max="15" width="21.142857142857142" customWidth="1"/>
-    <col min="16" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" customWidth="1"/>
+    <col min="16" max="24" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="5" t="s">
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="23"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="N4" s="6" t="s">
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="N4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="8">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10">
-        <v>1.1</v>
-      </c>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="13" t="s">
+      <c r="K5" s="34"/>
+      <c r="L5" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="4">
         <v>1.2</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="32"/>
+      <c r="G6" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="13"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10">
+      <c r="K6" s="34"/>
+      <c r="L6" s="35"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="4">
         <v>1.3</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="32"/>
+      <c r="G7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="13"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10">
+      <c r="K7" s="34"/>
+      <c r="L7" s="35"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="4">
         <v>1.4</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="32"/>
+      <c r="G8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="13"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10">
+      <c r="K8" s="34"/>
+      <c r="L8" s="35"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="4">
         <v>1.5</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="32"/>
+      <c r="G9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10">
+      <c r="K9" s="34"/>
+      <c r="L9" s="35"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="4">
         <v>1.6</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="32"/>
+      <c r="G10" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="13"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K10" s="34"/>
+      <c r="L10" s="35"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>2</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="15">
-        <v>1.1</v>
-      </c>
-      <c r="E11" s="12" t="s">
+      <c r="D11" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>3</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="17">
+      <c r="D12" s="14"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="15">
         <v>4</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="19">
-        <v>1.1</v>
-      </c>
-      <c r="E13" s="20" t="s">
+      <c r="D13" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19">
+      <c r="F13" s="32"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="6">
         <v>1.2</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="8">
+      <c r="F14" s="32"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="11">
         <v>5</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="10">
-        <v>1.1</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E15" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10">
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="4">
         <v>1.2</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10">
+      <c r="F16" s="32"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="4">
         <v>1.3</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="21">
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="17">
         <v>6</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="23">
-        <v>1.1</v>
-      </c>
-      <c r="E18" s="24" t="s">
+      <c r="D18" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E18" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="21"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="23">
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="7">
         <v>1.2</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="21"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23">
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="7">
         <v>1.3</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="21"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="23">
+      <c r="F20" s="32"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="7">
         <v>1.4</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="1">
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="10">
         <v>7</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="10">
-        <v>1.1</v>
-      </c>
-      <c r="E22" s="7" t="s">
+      <c r="D22" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E22" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="10">
+      <c r="F22" s="32"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="10"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="4">
         <v>1.2</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="1"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="10">
+      <c r="F23" s="32"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="10"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="4">
         <v>1.3</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="10">
+      <c r="F24" s="32"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="10"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="4">
         <v>1.4</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="26">
+      <c r="F25" s="32"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="20">
         <v>8</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="28">
-        <v>1.1</v>
+      <c r="D26" s="8">
+        <v>1.1000000000000001</v>
       </c>
       <c r="E26" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28">
+      <c r="F26" s="32"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="8">
         <v>1.2</v>
       </c>
       <c r="E27" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="26"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28">
+      <c r="F27" s="32"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="8">
         <v>1.3</v>
       </c>
       <c r="E28" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="28">
+      <c r="F28" s="32"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="8">
         <v>1.4</v>
       </c>
       <c r="E29" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="28">
+      <c r="F29" s="32"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="20"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="8">
         <v>1.5</v>
       </c>
       <c r="E30" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28">
+      <c r="F30" s="32"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="8">
         <v>1.6</v>
       </c>
       <c r="E31" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="C26:C31"/>
     <mergeCell ref="B5:B10"/>
     <mergeCell ref="C5:C10"/>
     <mergeCell ref="F5:F31"/>
@@ -1346,11 +1389,16 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C21"/>
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>